--- a/InputData/hydgn/HPSD/Hydgn Prod Subsidy Duration.xlsx
+++ b/InputData/hydgn/HPSD/Hydgn Prod Subsidy Duration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\hydgn\HPSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\HPSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405BBAF1-F6AD-418E-9379-83C6D6F4F3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AD4F92-DED8-4187-ADF9-CAD81D2B383D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1010" yWindow="410" windowWidth="17240" windowHeight="10830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Sources:</t>
   </si>
@@ -59,16 +62,40 @@
     <t>Unit: years</t>
   </si>
   <si>
-    <t>subsidy duration</t>
-  </si>
-  <si>
     <t>years</t>
   </si>
   <si>
-    <t xml:space="preserve">As a default, we use ten years to match the U.S. 45V scheme. </t>
-  </si>
-  <si>
     <t>HPSD Hydrogen Production Subsidy Duration</t>
+  </si>
+  <si>
+    <t>electrolysis</t>
+  </si>
+  <si>
+    <t>natural gas reforming</t>
+  </si>
+  <si>
+    <t>coal gasification</t>
+  </si>
+  <si>
+    <t>biomass gasification</t>
+  </si>
+  <si>
+    <t>hydrocarbon partial oxidation</t>
+  </si>
+  <si>
+    <t>electrolysis with guaranteed clean electricity</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
+  </si>
+  <si>
+    <t>Durations by pathway (2026-10-23). EPS reads one value per hydrogen production pathway.</t>
+  </si>
+  <si>
+    <t>45V clean hydrogen credit period (years), 26 U.S.C. 45V(a)(1)</t>
+  </si>
+  <si>
+    <t>45Q credit period (years), 26 U.S.C. 45Q(a)(3): blue hydrogen (SMR+CCS) is modeled as claiming 45Q, not 45V; the two cannot be combined</t>
   </si>
 </sst>
 </file>
@@ -120,14 +147,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="65.140625" customWidth="1"/>
@@ -416,7 +442,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -438,13 +464,29 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -458,7 +500,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
@@ -470,15 +512,70 @@
         <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <f>About!B12</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <f>About!B12</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <f>About!B12</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <f>About!B12</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <f>About!B12</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <f>About!B12</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <f>About!B13</f>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
